--- a/expense_details.xlsx
+++ b/expense_details.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:D10"/>
+  <dimension ref="A1:D11"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -485,63 +485,77 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>Transport</v>
+        <v>Shopping</v>
       </c>
       <c r="B7">
-        <v>4999</v>
+        <v>2323</v>
       </c>
       <c r="C7" t="str">
-        <v>2026-02-23</v>
+        <v>2026-02-26</v>
       </c>
       <c r="D7" t="str">
-        <v>🚗</v>
+        <v>🛍️</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>Shopping</v>
+        <v>Transport</v>
       </c>
       <c r="B8">
-        <v>7889</v>
+        <v>4999</v>
       </c>
       <c r="C8" t="str">
         <v>2026-02-23</v>
       </c>
       <c r="D8" t="str">
-        <v>🛍️</v>
+        <v>🚗</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>loss</v>
+        <v>Shopping</v>
       </c>
       <c r="B9">
-        <v>400078</v>
+        <v>7889</v>
       </c>
       <c r="C9" t="str">
-        <v>2026-02-16</v>
+        <v>2026-02-23</v>
       </c>
       <c r="D9" t="str">
-        <v>💸</v>
+        <v>🛍️</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="str">
+        <v>loss</v>
+      </c>
+      <c r="B10">
+        <v>400078</v>
+      </c>
+      <c r="C10" t="str">
+        <v>2026-02-16</v>
+      </c>
+      <c r="D10" t="str">
+        <v>💸</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="str">
         <v>Transport</v>
       </c>
-      <c r="B10">
+      <c r="B11">
         <v>5000</v>
       </c>
-      <c r="C10" t="str">
+      <c r="C11" t="str">
         <v>2026-02-09</v>
       </c>
-      <c r="D10" t="str">
+      <c r="D11" t="str">
         <v>🚗</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:D10"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:D11"/>
   </ignoredErrors>
 </worksheet>
 </file>